--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,36</t>
+          <t>-1,3; 9,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 19,16</t>
+          <t>-12,02; 17,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 7,89</t>
+          <t>-17,1; 8,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 3,07</t>
+          <t>-11,21; 2,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,24 +685,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 246,99</t>
+          <t>-66,04; 267,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 68,37</t>
+          <t>-67,14; 75,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,06; 127,2</t>
+          <t>-90,85; 91,59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 4,47</t>
+          <t>-12,88; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 4,39</t>
+          <t>-11,94; 4,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 14,98</t>
+          <t>-1,96; 14,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -1,76</t>
+          <t>-14,26; -1,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,35; 84,45</t>
+          <t>-79,55; 57,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,2; 81,9</t>
+          <t>-82,81; 105,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 303,48</t>
+          <t>-19,37; 304,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,88; -13,95</t>
+          <t>-90,53; -3,19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 5,14</t>
+          <t>-9,7; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 8,31</t>
+          <t>-7,16; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 4,96</t>
+          <t>-7,43; 4,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 17,62</t>
+          <t>-1,76; 19,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 100,27</t>
+          <t>-78,19; 105,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,26; 470,41</t>
+          <t>-100,0; 468,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 540,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 332,51</t>
+          <t>-20,86; 350,06</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 7,13</t>
+          <t>-6,59; 7,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 3,89</t>
+          <t>-14,12; 3,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 18,09</t>
+          <t>-7,73; 15,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 5,76</t>
+          <t>-9,02; 5,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,91; 234,9</t>
+          <t>-71,14; 320,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,84; 156,38</t>
+          <t>-90,51; 127,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 254,32</t>
+          <t>-48,54; 235,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,2; —</t>
+          <t>-96,55; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 37,03</t>
+          <t>-12,04; 36,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 12,87</t>
+          <t>-22,59; 13,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 14,67</t>
+          <t>-5,87; 15,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 2,63</t>
+          <t>-18,26; 2,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 236,11</t>
+          <t>-100,0; 309,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 13,43</t>
+          <t>0,19; 12,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 5,08</t>
+          <t>-7,79; 5,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 13,78</t>
+          <t>-0,0; 14,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -2,0</t>
+          <t>-22,23; -2,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,27; 0,5</t>
+          <t>-100,0; -3,91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,13</t>
+          <t>-7,9; 5,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 11,34</t>
+          <t>-3,03; 12,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,35</t>
+          <t>-6,12; 2,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,63</t>
+          <t>-9,18; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 71,21</t>
+          <t>-62,4; 88,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 139,55</t>
+          <t>-20,34; 157,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-79,71; 111,09</t>
+          <t>-83,92; 91,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 64,21</t>
+          <t>-55,15; 46,01</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -1,26</t>
+          <t>-14,57; -2,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 10,73</t>
+          <t>-1,41; 10,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 10,06</t>
+          <t>1,23; 10,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,34</t>
+          <t>-0,95; 4,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,58; -8,08</t>
+          <t>-88,2; -15,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 219,62</t>
+          <t>-20,21; 217,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 725,23</t>
+          <t>3,92; 762,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,43; —</t>
+          <t>-82,55; 1074,05</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,18</t>
+          <t>-4,12; 1,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,0</t>
+          <t>-1,99; 4,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,42</t>
+          <t>-0,83; 4,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,18</t>
+          <t>-5,03; 0,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 18,0</t>
+          <t>-44,5; 18,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 52,1</t>
+          <t>-18,66; 54,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 81,97</t>
+          <t>-10,93; 86,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 5,05</t>
+          <t>-50,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 9,64</t>
+          <t>-1,38; 9,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 17,09</t>
+          <t>-15,48; 14,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 8,59</t>
+          <t>-18,52; 8,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 2,09</t>
+          <t>-11,0; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 267,1</t>
+          <t>-77,9; 193,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 75,98</t>
+          <t>-72,02; 74,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,85; 91,59</t>
+          <t>-90,9; 112,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 3,39</t>
+          <t>-12,27; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 4,61</t>
+          <t>-11,63; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 14,87</t>
+          <t>-1,79; 15,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -1,23</t>
+          <t>-13,75; -1,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 57,96</t>
+          <t>-76,55; 70,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 105,44</t>
+          <t>-84,01; 82,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 304,99</t>
+          <t>-19,34; 288,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,53; -3,19</t>
+          <t>-90,08; -18,05</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 5,26</t>
+          <t>-9,29; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 7,78</t>
+          <t>-6,51; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 4,86</t>
+          <t>-6,84; 5,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 19,07</t>
+          <t>-3,62; 16,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 105,61</t>
+          <t>-75,95; 105,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 468,84</t>
+          <t>-84,28; 384,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 412,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 350,06</t>
+          <t>-30,86; 293,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 7,25</t>
+          <t>-6,77; 7,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 3,7</t>
+          <t>-14,75; 3,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 15,93</t>
+          <t>-8,1; 16,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 5,82</t>
+          <t>-9,38; 5,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 320,26</t>
+          <t>-73,92; 264,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,51; 127,48</t>
+          <t>-100,0; 122,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 235,65</t>
+          <t>-46,82; 246,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-96,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 36,61</t>
+          <t>-6,32; 37,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 13,36</t>
+          <t>-23,17; 12,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 15,75</t>
+          <t>-5,89; 15,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 2,67</t>
+          <t>-14,93; 2,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 309,88</t>
+          <t>-100,0; 179,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,85; inf</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 12,1</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 5,04</t>
+          <t>-7,78; 5,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 14,67</t>
+          <t>-0,0; 16,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,23; -2,42</t>
+          <t>-21,07; -2,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,91</t>
+          <t>-95,18; 22,84</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,25</t>
+          <t>-7,5; 4,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 12,28</t>
+          <t>-3,17; 12,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 2,08</t>
+          <t>-5,84; 2,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 4,49</t>
+          <t>-9,36; 4,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 88,02</t>
+          <t>-62,97; 74,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 157,64</t>
+          <t>-23,6; 153,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 91,86</t>
+          <t>-82,31; 110,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,15; 46,01</t>
+          <t>-53,02; 42,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -2,0</t>
+          <t>-14,42; -1,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,62</t>
+          <t>-1,53; 10,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,23</t>
+          <t>1,23; 9,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,01</t>
+          <t>-0,76; 4,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,2; -15,55</t>
+          <t>-89,25; -6,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 217,49</t>
+          <t>-20,63; 204,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 762,36</t>
+          <t>9,45; 657,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,55; 1074,05</t>
+          <t>-80,48; —</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,23</t>
+          <t>-3,99; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,26</t>
+          <t>-1,8; 4,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,66</t>
+          <t>-0,79; 4,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,28</t>
+          <t>-4,63; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 18,72</t>
+          <t>-43,1; 19,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 54,7</t>
+          <t>-17,64; 56,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 86,24</t>
+          <t>-9,91; 88,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 5,59</t>
+          <t>-49,08; 5,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-49,23%</t>
+          <t>-36,57%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 9,38</t>
+          <t>-0,98; 10,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 14,58</t>
+          <t>-11,96; 19,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 8,88</t>
+          <t>-17,72; 7,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 2,46</t>
+          <t>-8,38; 4,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,9; 193,18</t>
+          <t>-67,55; 246,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 74,85</t>
+          <t>-66,93; 68,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-90,9; 112,87</t>
+          <t>-87,04; 222,32</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,52</t>
+          <t>-6,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-66,3%</t>
+          <t>-55,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 3,68</t>
+          <t>-11,78; 4,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 4,1</t>
+          <t>-12,4; 4,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 15,77</t>
+          <t>-0,94; 14,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -1,76</t>
+          <t>-13,87; -0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 70,69</t>
+          <t>-76,35; 84,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 82,43</t>
+          <t>-82,2; 81,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 288,39</t>
+          <t>-17,41; 303,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,08; -18,05</t>
+          <t>-84,41; 9,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 5,55</t>
+          <t>-10,01; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 7,49</t>
+          <t>-7,05; 8,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 5,25</t>
+          <t>-7,38; 4,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,58</t>
+          <t>-2,04; 17,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,95; 105,0</t>
+          <t>-79,44; 100,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 384,39</t>
+          <t>-84,26; 470,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 412,74</t>
+          <t>-100,0; 540,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 293,84</t>
+          <t>-26,14; 333,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,56%</t>
+          <t>-35,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 7,73</t>
+          <t>-7,37; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 3,74</t>
+          <t>-14,39; 3,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 16,52</t>
+          <t>-7,46; 18,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 5,95</t>
+          <t>-11,09; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 264,51</t>
+          <t>-80,91; 234,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,41</t>
+          <t>-89,84; 156,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 246,26</t>
+          <t>-46,68; 254,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 441,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-66,08%</t>
+          <t>-8,04%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 37,04</t>
+          <t>-11,68; 37,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 12,08</t>
+          <t>-23,69; 12,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 15,6</t>
+          <t>-6,66; 14,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 2,59</t>
+          <t>-5,23; 3,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 179,68</t>
+          <t>-100,0; 236,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-76,85; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,73</t>
+          <t>-11,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-75,97%</t>
+          <t>-78,47%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,17; 13,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 5,02</t>
+          <t>-8,83; 5,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 16,13</t>
+          <t>-0,0; 13,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -2,15</t>
+          <t>-22,43; -2,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,18; 22,84</t>
+          <t>-95,87; -4,45</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>-13,7%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 4,26</t>
+          <t>-7,78; 4,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 12,22</t>
+          <t>-3,14; 11,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 2,47</t>
+          <t>-6,29; 2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 4,14</t>
+          <t>-8,82; 6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,97; 74,92</t>
+          <t>-61,47; 71,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 153,67</t>
+          <t>-24,57; 139,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-82,31; 110,89</t>
+          <t>-79,71; 111,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 42,17</t>
+          <t>-50,65; 68,18</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>114,0%</t>
+          <t>217,47%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -1,26</t>
+          <t>-14,39; -1,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,2</t>
+          <t>-1,43; 10,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,81</t>
+          <t>1,37; 10,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,28</t>
+          <t>-0,2; 5,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,25; -6,88</t>
+          <t>-87,58; -8,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 204,34</t>
+          <t>-16,9; 219,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 657,09</t>
+          <t>12,16; 725,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,48; —</t>
+          <t>-72,84; —</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-26,86%</t>
+          <t>-19,0%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,22</t>
+          <t>-3,97; 1,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,17</t>
+          <t>-2,11; 4,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,68</t>
+          <t>-0,73; 4,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,45</t>
+          <t>-4,02; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 19,28</t>
+          <t>-42,67; 18,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 56,1</t>
+          <t>-19,37; 52,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 88,26</t>
+          <t>-9,69; 81,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 5,79</t>
+          <t>-43,09; 14,84</t>
         </is>
       </c>
     </row>
